--- a/static/bulk_upload_template.xlsx
+++ b/static/bulk_upload_template.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -536,6 +536,11 @@
           <t>is_urdu</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -596,6 +601,7 @@
           <t>no</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -749,9 +755,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/static/bulk_upload_template.xlsx
+++ b/static/bulk_upload_template.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,15 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="001B5E20"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
     </font>
   </fonts>
   <fills count="4">
@@ -49,16 +39,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5AAC"/>
+        <fgColor rgb="001F5C99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EC"/>
+        <fgColor rgb="003B7DC8"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -66,33 +56,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D6DEEA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D6DEEA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D6DEEA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D6DEEA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,373 +433,353 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>option_d</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>marks</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>subject</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>topic</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>is_urdu</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>mcq</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>What is the chemical formula of water?</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>H2O</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>CO2</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>NaCl</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Science</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Water Cycle</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>tf</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>The Earth revolves around the Sun.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Science</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Solar System</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>fill</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>The capital of Pakistan is ___.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Islamabad</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Pakistan Studies</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Cities</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Explain the process of photosynthesis.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Plants</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Bulk Upload — Instructions</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>option_c</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>option_d</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>marks</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>is_urdu</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>bloom_level</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>keywords</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>learning_outcome</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>estimated_time</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>source_book</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>page_number</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>What is H2O?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Salt</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sugar</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Water Cycle</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>REMEMBER</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>water, chemistry</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Students can identify water.</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>NCERT Science 5</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>45</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. 'Questions' sheet mein data bharo. Header row mat hataana.</t>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Explain the water cycle.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Water Cycle</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>UNDERSTAND</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>water cycle, evaporation</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NCERT Science 6</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>published</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Green sample rows sirf example hain — HATAAO ya replace karo apne data se.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3. type column: mcq / fill / tf / short (chhote harf mein)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4. MCQ mein option_a aur option_b zaroori hain. correct = a/b/c/d (letter).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5. tf mein correct = true ya false</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6. fill/short mein correct = jawab ka text (ya khaali chhod sakte ho)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7. marks khaali chhodo to default 1 lagega</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>8. is_urdu = yes agar sawal Urdu mein ho, warna no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>9. topic column mein syllabus topic ka naam likhein — agar match mila to link ho jayega</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10. Ek galat row se poori file fail nahi hogi — sirf woh row skip hogi</t>
-        </is>
-      </c>
+          <t>tf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Water boils at 100 degrees Celsius.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/bulk_upload_template.xlsx
+++ b/static/bulk_upload_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +50,12 @@
         <fgColor rgb="003B7DC8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,12 +69,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -433,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -457,6 +469,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,6 +578,11 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>answer_lines</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -625,7 +643,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>REMEMBER</t>
@@ -679,11 +696,6 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>2</v>
       </c>
@@ -702,7 +714,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>UNDERSTAND</t>
@@ -718,14 +729,11 @@
           <t>water cycle, evaporation</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>NCERT Science 6</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>published</t>
@@ -748,10 +756,6 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>true</t>
@@ -765,21 +769,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/bulk_upload_template.xlsx
+++ b/static/bulk_upload_template.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -583,6 +583,11 @@
           <t>answer_lines</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>slo_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -679,6 +684,7 @@
           <t>published</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -739,6 +745,11 @@
           <t>published</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SCI-01, SCI-02</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -774,6 +785,7 @@
           <t>no</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
